--- a/plans/reports/phase-03-family-c-verification/glorex-t3-2026-customs-final.xlsx
+++ b/plans/reports/phase-03-family-c-verification/glorex-t3-2026-customs-final.xlsx
@@ -233,7 +233,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="857250" cy="857250"/>
+    <ext cx="2095500" cy="685800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -263,7 +263,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="857250" cy="857250"/>
+    <ext cx="2095500" cy="685800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
